--- a/real_estate_forms/012_tenant_satisfaction_survey--real_estate_forms.xlsx
+++ b/real_estate_forms/012_tenant_satisfaction_survey--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pool</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pool</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
@@ -1087,46 +1087,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gym</t>
+          <t>laundry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gym</t>
+          <t>Laundry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>amenities_list_choices</t>
+          <t>communication_channels_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>laundry</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Laundry</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>amenities_list_choices</t>
+          <t>communication_channels_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1138,46 +1138,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>emergency_contacts_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>property_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Property Manager</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>emergency_contacts_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>property_owner</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Property Owner</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>property_manager</t>
+          <t>maintenance_worker</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Property Manager</t>
+          <t>Maintenance Worker</t>
         </is>
       </c>
     </row>
@@ -1206,46 +1206,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>property_owner</t>
+          <t>emergency_services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Property Owner</t>
+          <t>Emergency Services</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emergency_contacts_choices</t>
+          <t>emergency_contacts_list_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>maintenance_worker</t>
+          <t>property_manager</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maintenance Worker</t>
+          <t>Property Manager</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emergency_contacts_choices</t>
+          <t>emergency_contacts_list_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>emergency_services</t>
+          <t>property_owner</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Emergency Services</t>
+          <t>Property Owner</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>property_manager</t>
+          <t>maintenance_worker</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Property Manager</t>
+          <t>Maintenance Worker</t>
         </is>
       </c>
     </row>
@@ -1274,46 +1274,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>property_owner</t>
+          <t>emergency_services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Property Owner</t>
+          <t>Emergency Services</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emergency_contacts_list_choices</t>
+          <t>preferred_mode_of_contact_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>maintenance_worker</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Maintenance Worker</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emergency_contacts_list_choices</t>
+          <t>preferred_mode_of_contact_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>emergency_services</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency Services</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1325,46 +1325,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>preferred_mode_of_contact_choices</t>
+          <t>contact_frequency_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>preferred_mode_of_contact_choices</t>
+          <t>contact_frequency_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bi-weekly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
@@ -1444,44 +1444,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>contact_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>semi-annually</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Semi-Annually</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>contact_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>annually</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>Annually</t>
         </is>
